--- a/public/master-data.xlsx
+++ b/public/master-data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="98">
   <si>
     <t>session</t>
   </si>
@@ -57,12 +57,6 @@
     <t>9th</t>
   </si>
   <si>
-    <t>2023-24</t>
-  </si>
-  <si>
-    <t>2024-25</t>
-  </si>
-  <si>
     <t>WARPORA</t>
   </si>
   <si>
@@ -310,6 +304,12 @@
   </si>
   <si>
     <t>maxMarks</t>
+  </si>
+  <si>
+    <t>KULSOOMA AKHTER</t>
+  </si>
+  <si>
+    <t>MOHAMMAD MAQBOOL LONE</t>
   </si>
 </sst>
 </file>
@@ -374,7 +374,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -442,11 +442,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -485,6 +496,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -788,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
@@ -797,16 +820,16 @@
   <sheetData>
     <row r="1" spans="1:19" ht="27.6" thickBot="1">
       <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -824,7 +847,7 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
@@ -836,7 +859,7 @@
         <v>7</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -845,10 +868,10 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>10</v>
@@ -864,11 +887,11 @@
       <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>14</v>
+      <c r="D2" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E2" s="5">
+        <v>2025</v>
       </c>
       <c r="F2" s="5">
         <v>21853031402</v>
@@ -877,13 +900,13 @@
         <v>40964</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="K2" s="3">
         <v>88</v>
@@ -923,11 +946,11 @@
       <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
+      <c r="D3" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2025</v>
       </c>
       <c r="F3" s="5">
         <v>22081888047</v>
@@ -936,13 +959,13 @@
         <v>40221</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K3" s="3">
         <v>87</v>
@@ -982,11 +1005,11 @@
       <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>14</v>
+      <c r="D4" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2025</v>
       </c>
       <c r="F4" s="5">
         <v>21889774740</v>
@@ -995,13 +1018,13 @@
         <v>40910</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K4" s="3">
         <v>69</v>
@@ -1041,11 +1064,11 @@
       <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
+      <c r="D5" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2025</v>
       </c>
       <c r="F5" s="5">
         <v>22314685931</v>
@@ -1054,13 +1077,13 @@
         <v>40599</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K5" s="3">
         <v>88</v>
@@ -1095,16 +1118,16 @@
         <v>240805</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>14</v>
+      <c r="D6" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2025</v>
       </c>
       <c r="F6" s="5">
         <v>22381015809</v>
@@ -1113,13 +1136,13 @@
         <v>40882</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K6" s="3">
         <v>81</v>
@@ -1154,16 +1177,16 @@
         <v>240701</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2025</v>
       </c>
       <c r="F7" s="3">
         <v>22458230247</v>
@@ -1172,13 +1195,13 @@
         <v>41281</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K7" s="3">
         <v>85</v>
@@ -1213,16 +1236,16 @@
         <v>240702</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2025</v>
       </c>
       <c r="F8" s="3">
         <v>22330542156</v>
@@ -1231,13 +1254,13 @@
         <v>41597</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K8" s="3">
         <v>95</v>
@@ -1272,16 +1295,16 @@
         <v>240703</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2025</v>
       </c>
       <c r="F9" s="3">
         <v>21963244365</v>
@@ -1290,13 +1313,13 @@
         <v>41308</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K9" s="3">
         <v>88</v>
@@ -1331,16 +1354,16 @@
         <v>240704</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E10" s="5">
+        <v>2025</v>
       </c>
       <c r="F10" s="3">
         <v>21845123308</v>
@@ -1349,13 +1372,13 @@
         <v>40975</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K10" s="3">
         <v>84</v>
@@ -1390,16 +1413,16 @@
         <v>240705</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2025</v>
       </c>
       <c r="F11" s="3">
         <v>21893354918</v>
@@ -1408,13 +1431,13 @@
         <v>41054</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K11" s="3">
         <v>93</v>
@@ -1449,16 +1472,16 @@
         <v>240706</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="5">
+        <v>2025</v>
       </c>
       <c r="F12" s="3">
         <v>21829052544</v>
@@ -1467,13 +1490,13 @@
         <v>41194</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K12" s="3">
         <v>77</v>
@@ -1508,16 +1531,16 @@
         <v>240707</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2025</v>
       </c>
       <c r="F13" s="3">
         <v>22469492015</v>
@@ -1526,13 +1549,13 @@
         <v>41350</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K13" s="3">
         <v>89</v>
@@ -1567,16 +1590,16 @@
         <v>240708</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2025</v>
       </c>
       <c r="F14" s="3">
         <v>22156779194</v>
@@ -1585,13 +1608,13 @@
         <v>41194</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K14" s="3">
         <v>84</v>
@@ -1626,16 +1649,16 @@
         <v>240709</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2025</v>
       </c>
       <c r="F15" s="3">
         <v>21826564923</v>
@@ -1644,13 +1667,13 @@
         <v>41277</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K15" s="3">
         <v>89</v>
@@ -1685,16 +1708,16 @@
         <v>240601</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E16" s="5">
+        <v>2025</v>
       </c>
       <c r="F16" s="3">
         <v>22357047006</v>
@@ -1703,13 +1726,13 @@
         <v>41761</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K16" s="3">
         <v>92</v>
@@ -1744,16 +1767,16 @@
         <v>240501</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>14</v>
+        <v>44</v>
+      </c>
+      <c r="D17" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2025</v>
       </c>
       <c r="F17" s="3">
         <v>22121023828</v>
@@ -1762,13 +1785,13 @@
         <v>41758</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K17" s="3">
         <v>83</v>
@@ -1803,16 +1826,16 @@
         <v>240502</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>14</v>
+        <v>44</v>
+      </c>
+      <c r="D18" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E18" s="5">
+        <v>2025</v>
       </c>
       <c r="F18" s="3">
         <v>21868912548</v>
@@ -1821,13 +1844,13 @@
         <v>42009</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K18" s="3">
         <v>94</v>
@@ -1862,16 +1885,16 @@
         <v>240503</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>14</v>
+        <v>44</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E19" s="5">
+        <v>2025</v>
       </c>
       <c r="F19" s="3">
         <v>22069597962</v>
@@ -1880,13 +1903,13 @@
         <v>41841</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K19" s="3">
         <v>92</v>
@@ -1921,16 +1944,16 @@
         <v>240504</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>14</v>
+        <v>44</v>
+      </c>
+      <c r="D20" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2025</v>
       </c>
       <c r="F20" s="3">
         <v>22153782351</v>
@@ -1939,13 +1962,13 @@
         <v>42009</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K20" s="3">
         <v>86</v>
@@ -1980,16 +2003,16 @@
         <v>240505</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>14</v>
+        <v>44</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E21" s="5">
+        <v>2025</v>
       </c>
       <c r="F21" s="3">
         <v>21920555127</v>
@@ -1998,13 +2021,13 @@
         <v>41937</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -2027,16 +2050,16 @@
         <v>240506</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>14</v>
+        <v>44</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E22" s="5">
+        <v>2025</v>
       </c>
       <c r="F22" s="3">
         <v>22014784961</v>
@@ -2045,13 +2068,13 @@
         <v>42007</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -2074,16 +2097,16 @@
         <v>240507</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>14</v>
+        <v>44</v>
+      </c>
+      <c r="D23" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2025</v>
       </c>
       <c r="F23" s="3">
         <v>22527876769</v>
@@ -2092,13 +2115,13 @@
         <v>41768</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -2121,16 +2144,16 @@
         <v>240401</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="D24" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2025</v>
       </c>
       <c r="F24" s="3">
         <v>22462078881</v>
@@ -2139,13 +2162,13 @@
         <v>42326</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K24" s="3">
         <v>90</v>
@@ -2180,16 +2203,16 @@
         <v>240402</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="D25" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E25" s="5">
+        <v>2025</v>
       </c>
       <c r="F25" s="3">
         <v>22035600261</v>
@@ -2198,13 +2221,13 @@
         <v>42139</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K25" s="3">
         <v>93</v>
@@ -2236,19 +2259,19 @@
     </row>
     <row r="26" spans="1:19" ht="56.4" thickBot="1">
       <c r="A26" s="3">
-        <v>240402</v>
+        <v>240403</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="D26" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E26" s="5">
+        <v>2025</v>
       </c>
       <c r="F26" s="3">
         <v>22134434507</v>
@@ -2257,13 +2280,13 @@
         <v>42141</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K26" s="3">
         <v>95</v>
@@ -2298,16 +2321,16 @@
         <v>240301</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
+      </c>
+      <c r="D27" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E27" s="5">
+        <v>2025</v>
       </c>
       <c r="F27" s="3">
         <v>22406593813</v>
@@ -2316,13 +2339,13 @@
         <v>42829</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K27" s="3">
         <v>94</v>
@@ -2357,16 +2380,16 @@
         <v>240302</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
+      </c>
+      <c r="D28" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E28" s="5">
+        <v>2025</v>
       </c>
       <c r="F28" s="3">
         <v>21922872700</v>
@@ -2375,13 +2398,13 @@
         <v>42370</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K28" s="3">
         <v>84</v>
@@ -2416,16 +2439,16 @@
         <v>240303</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
+      </c>
+      <c r="D29" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E29" s="5">
+        <v>2025</v>
       </c>
       <c r="F29" s="3">
         <v>22382305783</v>
@@ -2434,13 +2457,13 @@
         <v>43053</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K29" s="3">
         <v>99</v>
@@ -2475,16 +2498,16 @@
         <v>240201</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="D30" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E30" s="5">
+        <v>2025</v>
       </c>
       <c r="F30" s="3">
         <v>22442259018</v>
@@ -2493,13 +2516,13 @@
         <v>43052</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K30" s="3">
         <v>95</v>
@@ -2534,16 +2557,16 @@
         <v>240202</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>14</v>
+        <v>68</v>
+      </c>
+      <c r="D31" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E31" s="5">
+        <v>2025</v>
       </c>
       <c r="F31" s="3">
         <v>21997522265</v>
@@ -2552,13 +2575,13 @@
         <v>42448</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K31" s="3">
         <v>88</v>
@@ -2593,16 +2616,16 @@
         <v>240101</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>14</v>
+        <v>76</v>
+      </c>
+      <c r="D32" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E32" s="5">
+        <v>2025</v>
       </c>
       <c r="F32" s="3">
         <v>22380063014</v>
@@ -2611,13 +2634,13 @@
         <v>43169</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K32" s="3">
         <v>96</v>
@@ -2652,16 +2675,16 @@
         <v>240102</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>14</v>
+        <v>76</v>
+      </c>
+      <c r="D33" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E33" s="5">
+        <v>2025</v>
       </c>
       <c r="F33" s="3">
         <v>22560361322</v>
@@ -2670,13 +2693,13 @@
         <v>43318</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K33" s="3">
         <v>89</v>
@@ -2711,16 +2734,16 @@
         <v>240103</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>14</v>
+        <v>76</v>
+      </c>
+      <c r="D34" s="5">
+        <v>2024</v>
+      </c>
+      <c r="E34" s="5">
+        <v>2025</v>
       </c>
       <c r="F34" s="3">
         <v>22669784529</v>
@@ -2729,13 +2752,13 @@
         <v>43206</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K34" s="3">
         <v>84</v>
@@ -2763,6 +2786,62 @@
       </c>
       <c r="S34" s="3">
         <v>86.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="69.599999999999994">
+      <c r="A35" s="14">
+        <v>160802</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="16">
+        <v>2016</v>
+      </c>
+      <c r="E35" s="16">
+        <v>2016</v>
+      </c>
+      <c r="F35" s="14">
+        <v>160802</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="K35" s="14">
+        <v>82</v>
+      </c>
+      <c r="L35" s="14">
+        <v>80</v>
+      </c>
+      <c r="M35" s="14">
+        <v>82</v>
+      </c>
+      <c r="N35" s="14">
+        <v>82</v>
+      </c>
+      <c r="O35" s="14">
+        <v>84</v>
+      </c>
+      <c r="P35" s="14">
+        <v>90</v>
+      </c>
+      <c r="Q35" s="14">
+        <v>500</v>
+      </c>
+      <c r="R35" s="14">
+        <v>600</v>
+      </c>
+      <c r="S35" s="14">
+        <v>83.33</v>
       </c>
     </row>
   </sheetData>
